--- a/ZANSHIN/進捗コスト表.xlsx
+++ b/ZANSHIN/進捗コスト表.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30131"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30228"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\HiromatsuKengo\Desktop\ZANSHIN\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\PC_User\Documents\GitHub\KengoSchoole\ZANSHIN\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D05D874B-A552-409D-85C3-C2088C726649}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{70A78409-24E6-4E6C-8C6E-03ED9F67D52F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="4230" yWindow="915" windowWidth="21600" windowHeight="11295" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="2670" yWindow="3585" windowWidth="21600" windowHeight="11295" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="仕様" sheetId="1" r:id="rId1"/>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="60" uniqueCount="50">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="80" uniqueCount="50">
   <si>
     <t>1コスト:3時間 (1日は基本2コスト)</t>
   </si>
@@ -464,7 +464,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="13">
+  <fills count="14">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -537,6 +537,12 @@
         <bgColor rgb="FF000000"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.39997558519241921"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="4">
     <border>
@@ -587,7 +593,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="23">
+  <cellXfs count="24">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="56" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="176" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
@@ -611,6 +617,7 @@
     <xf numFmtId="0" fontId="4" fillId="12" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="5" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="13" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="標準" xfId="0" builtinId="0"/>
@@ -891,7 +898,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:L89"/>
+  <dimension ref="A1:L88"/>
   <sheetFormatPr defaultRowHeight="18.75"/>
   <cols>
     <col min="1" max="1" width="9.25" customWidth="1"/>
@@ -927,7 +934,7 @@
         <v>5</v>
       </c>
       <c r="H2">
-        <f>SUM(C3:C89)</f>
+        <f>SUM(C3:C88)</f>
         <v>24</v>
       </c>
     </row>
@@ -946,7 +953,7 @@
         <v>6</v>
       </c>
       <c r="H3">
-        <f>SUMIF(E3:E89,"完了",C3:C89)</f>
+        <f>SUMIF(E3:E88,"完了",C3:C88)</f>
         <v>0</v>
       </c>
       <c r="K3" t="s">
@@ -972,7 +979,7 @@
       </c>
       <c r="H4" s="2">
         <f ca="1">NETWORKDAYS(H5,H6)</f>
-        <v>475</v>
+        <v>4</v>
       </c>
       <c r="I4" t="s">
         <v>10</v>
@@ -983,7 +990,7 @@
       </c>
       <c r="K4" s="2">
         <f ca="1">_xlfn.DAYS(H6,H5)</f>
-        <v>662</v>
+        <v>3</v>
       </c>
       <c r="L4" s="3">
         <f ca="1">H3/K4</f>
@@ -1001,8 +1008,8 @@
         <v>11</v>
       </c>
       <c r="H5" s="1">
-        <f>DATE(2024,9,30)</f>
-        <v>45565</v>
+        <f>DATE(2026,7,27)</f>
+        <v>46230</v>
       </c>
     </row>
     <row r="6" spans="1:12">
@@ -1021,7 +1028,7 @@
       </c>
       <c r="H6" s="1">
         <f ca="1">TODAY()</f>
-        <v>46227</v>
+        <v>46233</v>
       </c>
     </row>
     <row r="7" spans="1:12">
@@ -1102,7 +1109,9 @@
       </c>
       <c r="C12" s="21"/>
       <c r="D12" s="21"/>
-      <c r="E12" s="21"/>
+      <c r="E12" s="21" t="s">
+        <v>30</v>
+      </c>
       <c r="G12" s="8" t="s">
         <v>17</v>
       </c>
@@ -1112,19 +1121,19 @@
       </c>
       <c r="I12" s="2">
         <f ca="1">NETWORKDAYS(TODAY(),H12)</f>
-        <v>21</v>
+        <v>17</v>
       </c>
       <c r="J12" s="3">
         <f ca="1">($H$2 - $H$3) / I12</f>
-        <v>1.1428571428571428</v>
+        <v>1.411764705882353</v>
       </c>
       <c r="K12">
         <f ca="1">_xlfn.DAYS(H12,$H$6)</f>
-        <v>30</v>
+        <v>24</v>
       </c>
       <c r="L12" s="3">
         <f ca="1">($H$2 - $H$3) / K12</f>
-        <v>0.8</v>
+        <v>1</v>
       </c>
     </row>
     <row r="13" spans="1:12">
@@ -1133,7 +1142,9 @@
       </c>
       <c r="C13" s="16"/>
       <c r="D13" s="16"/>
-      <c r="E13" s="16"/>
+      <c r="E13" s="16" t="s">
+        <v>21</v>
+      </c>
       <c r="G13" s="13" t="s">
         <v>18</v>
       </c>
@@ -1143,19 +1154,19 @@
       </c>
       <c r="I13" s="2">
         <f t="shared" ref="I13:I14" ca="1" si="0">NETWORKDAYS(TODAY(),H13)</f>
-        <v>26</v>
+        <v>22</v>
       </c>
       <c r="J13" s="3">
         <f ca="1">($H$2 - $H$3) / I13</f>
-        <v>0.92307692307692313</v>
+        <v>1.0909090909090908</v>
       </c>
       <c r="K13">
         <f t="shared" ref="K13:K14" ca="1" si="1">_xlfn.DAYS(H13,$H$6)</f>
-        <v>37</v>
+        <v>31</v>
       </c>
       <c r="L13" s="3">
         <f ca="1">($H$2 - $H$3) / K13</f>
-        <v>0.64864864864864868</v>
+        <v>0.77419354838709675</v>
       </c>
     </row>
     <row r="14" spans="1:12">
@@ -1164,7 +1175,9 @@
       </c>
       <c r="C14" s="16"/>
       <c r="D14" s="16"/>
-      <c r="E14" s="16"/>
+      <c r="E14" s="16" t="s">
+        <v>21</v>
+      </c>
       <c r="G14" s="14" t="s">
         <v>19</v>
       </c>
@@ -1174,19 +1187,19 @@
       </c>
       <c r="I14" s="2">
         <f t="shared" ca="1" si="0"/>
-        <v>28</v>
+        <v>24</v>
       </c>
       <c r="J14" s="3">
         <f ca="1">($H$2 - $H$3) / I14</f>
-        <v>0.8571428571428571</v>
+        <v>1</v>
       </c>
       <c r="K14">
         <f t="shared" ca="1" si="1"/>
-        <v>39</v>
+        <v>33</v>
       </c>
       <c r="L14" s="3">
         <f ca="1">($H$2 - $H$3) / K14</f>
-        <v>0.61538461538461542</v>
+        <v>0.72727272727272729</v>
       </c>
     </row>
     <row r="15" spans="1:12">
@@ -1195,7 +1208,9 @@
       </c>
       <c r="C15" s="16"/>
       <c r="D15" s="16"/>
-      <c r="E15" s="16"/>
+      <c r="E15" s="16" t="s">
+        <v>21</v>
+      </c>
       <c r="G15" s="15"/>
       <c r="H15" s="1"/>
       <c r="I15" s="2"/>
@@ -1208,7 +1223,9 @@
       </c>
       <c r="C16" s="16"/>
       <c r="D16" s="16"/>
-      <c r="E16" s="16"/>
+      <c r="E16" s="16" t="s">
+        <v>21</v>
+      </c>
     </row>
     <row r="17" spans="2:5">
       <c r="B17" s="16" t="s">
@@ -1216,7 +1233,9 @@
       </c>
       <c r="C17" s="16"/>
       <c r="D17" s="16"/>
-      <c r="E17" s="16"/>
+      <c r="E17" s="16" t="s">
+        <v>21</v>
+      </c>
     </row>
     <row r="18" spans="2:5">
       <c r="B18" s="16" t="s">
@@ -1224,7 +1243,9 @@
       </c>
       <c r="C18" s="16"/>
       <c r="D18" s="16"/>
-      <c r="E18" s="16"/>
+      <c r="E18" s="16" t="s">
+        <v>21</v>
+      </c>
     </row>
     <row r="19" spans="2:5">
       <c r="B19" s="16" t="s">
@@ -1232,7 +1253,9 @@
       </c>
       <c r="C19" s="16"/>
       <c r="D19" s="16"/>
-      <c r="E19" s="16"/>
+      <c r="E19" s="16" t="s">
+        <v>21</v>
+      </c>
     </row>
     <row r="20" spans="2:5">
       <c r="B20" s="16" t="s">
@@ -1240,7 +1263,9 @@
       </c>
       <c r="C20" s="16"/>
       <c r="D20" s="16"/>
-      <c r="E20" s="16"/>
+      <c r="E20" s="16" t="s">
+        <v>21</v>
+      </c>
     </row>
     <row r="21" spans="2:5">
       <c r="B21" s="16" t="s">
@@ -1248,15 +1273,17 @@
       </c>
       <c r="C21" s="16"/>
       <c r="D21" s="16"/>
-      <c r="E21" s="16"/>
+      <c r="E21" s="16" t="s">
+        <v>21</v>
+      </c>
     </row>
     <row r="22" spans="2:5">
-      <c r="B22" s="16" t="s">
+      <c r="B22" s="23" t="s">
         <v>44</v>
       </c>
-      <c r="C22" s="16"/>
-      <c r="D22" s="16"/>
-      <c r="E22" s="16"/>
+      <c r="C22" s="23"/>
+      <c r="D22" s="23"/>
+      <c r="E22" s="23"/>
     </row>
     <row r="23" spans="2:5">
       <c r="B23" s="16" t="s">
@@ -1264,7 +1291,9 @@
       </c>
       <c r="C23" s="16"/>
       <c r="D23" s="16"/>
-      <c r="E23" s="16"/>
+      <c r="E23" s="16" t="s">
+        <v>21</v>
+      </c>
     </row>
     <row r="24" spans="2:5">
       <c r="B24" s="16" t="s">
@@ -1272,7 +1301,9 @@
       </c>
       <c r="C24" s="16"/>
       <c r="D24" s="16"/>
-      <c r="E24" s="16"/>
+      <c r="E24" s="16" t="s">
+        <v>21</v>
+      </c>
     </row>
     <row r="25" spans="2:5">
       <c r="B25" s="16" t="s">
@@ -1280,7 +1311,9 @@
       </c>
       <c r="C25" s="16"/>
       <c r="D25" s="16"/>
-      <c r="E25" s="16"/>
+      <c r="E25" s="16" t="s">
+        <v>21</v>
+      </c>
     </row>
     <row r="26" spans="2:5">
       <c r="B26" s="22" t="s">
@@ -1296,7 +1329,9 @@
       </c>
       <c r="C27" s="16"/>
       <c r="D27" s="16"/>
-      <c r="E27" s="16"/>
+      <c r="E27" s="16" t="s">
+        <v>21</v>
+      </c>
     </row>
     <row r="28" spans="2:5">
       <c r="B28" s="16" t="s">
@@ -1304,7 +1339,9 @@
       </c>
       <c r="C28" s="16"/>
       <c r="D28" s="16"/>
-      <c r="E28" s="16"/>
+      <c r="E28" s="16" t="s">
+        <v>21</v>
+      </c>
     </row>
     <row r="29" spans="2:5">
       <c r="B29" s="16" t="s">
@@ -1312,7 +1349,9 @@
       </c>
       <c r="C29" s="16"/>
       <c r="D29" s="16"/>
-      <c r="E29" s="16"/>
+      <c r="E29" s="16" t="s">
+        <v>21</v>
+      </c>
     </row>
     <row r="30" spans="2:5">
       <c r="B30" s="16" t="s">
@@ -1320,7 +1359,9 @@
       </c>
       <c r="C30" s="16"/>
       <c r="D30" s="16"/>
-      <c r="E30" s="16"/>
+      <c r="E30" s="16" t="s">
+        <v>21</v>
+      </c>
     </row>
     <row r="31" spans="2:5">
       <c r="B31" s="16" t="s">
@@ -1328,34 +1369,40 @@
       </c>
       <c r="C31" s="16"/>
       <c r="D31" s="16"/>
-      <c r="E31" s="16"/>
+      <c r="E31" s="16" t="s">
+        <v>21</v>
+      </c>
     </row>
     <row r="32" spans="2:5">
-      <c r="B32" s="16"/>
-      <c r="C32" s="16"/>
-      <c r="D32" s="16"/>
-      <c r="E32" s="16"/>
+      <c r="B32" s="23" t="s">
+        <v>44</v>
+      </c>
+      <c r="C32" s="23"/>
+      <c r="D32" s="23"/>
+      <c r="E32" s="23"/>
     </row>
     <row r="33" spans="2:5">
       <c r="B33" s="16" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="C33" s="16"/>
       <c r="D33" s="16"/>
-      <c r="E33" s="16"/>
+      <c r="E33" s="16" t="s">
+        <v>21</v>
+      </c>
     </row>
     <row r="34" spans="2:5">
       <c r="B34" s="16" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="C34" s="16"/>
       <c r="D34" s="16"/>
-      <c r="E34" s="16"/>
+      <c r="E34" s="16" t="s">
+        <v>21</v>
+      </c>
     </row>
     <row r="35" spans="2:5">
-      <c r="B35" s="16" t="s">
-        <v>46</v>
-      </c>
+      <c r="B35" s="16"/>
       <c r="C35" s="16"/>
       <c r="D35" s="16"/>
       <c r="E35" s="16"/>
@@ -1563,6 +1610,7 @@
       <c r="C69" s="16"/>
       <c r="D69" s="16"/>
       <c r="E69" s="16"/>
+      <c r="G69" s="1"/>
     </row>
     <row r="70" spans="2:7">
       <c r="B70" s="16"/>
@@ -1590,7 +1638,6 @@
       <c r="C73" s="16"/>
       <c r="D73" s="16"/>
       <c r="E73" s="16"/>
-      <c r="G73" s="1"/>
     </row>
     <row r="74" spans="2:7">
       <c r="B74" s="16"/>
@@ -1635,16 +1682,16 @@
       <c r="E80" s="16"/>
     </row>
     <row r="81" spans="2:5">
-      <c r="B81" s="16"/>
-      <c r="C81" s="16"/>
-      <c r="D81" s="16"/>
-      <c r="E81" s="16"/>
+      <c r="B81" s="17"/>
+      <c r="C81" s="17"/>
+      <c r="D81" s="17"/>
+      <c r="E81" s="17"/>
     </row>
     <row r="82" spans="2:5">
-      <c r="B82" s="17"/>
-      <c r="C82" s="17"/>
-      <c r="D82" s="17"/>
-      <c r="E82" s="17"/>
+      <c r="B82" s="16"/>
+      <c r="C82" s="16"/>
+      <c r="D82" s="16"/>
+      <c r="E82" s="16"/>
     </row>
     <row r="83" spans="2:5">
       <c r="B83" s="16"/>
@@ -1681,12 +1728,6 @@
       <c r="C88" s="16"/>
       <c r="D88" s="16"/>
       <c r="E88" s="16"/>
-    </row>
-    <row r="89" spans="2:5">
-      <c r="B89" s="16"/>
-      <c r="C89" s="16"/>
-      <c r="D89" s="16"/>
-      <c r="E89" s="16"/>
     </row>
   </sheetData>
   <phoneticPr fontId="1"/>
@@ -1706,6 +1747,15 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="ドキュメント" ma:contentTypeID="0x010100916D42E3690EEE418172DBF4B6395129" ma:contentTypeVersion="32" ma:contentTypeDescription="新しいドキュメントを作成します。" ma:contentTypeScope="" ma:versionID="2bec52062c397840dce5bfa38caf7040">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="c7208212-5067-493a-8683-cc3386cb0efe" xmlns:ns3="b9cacb4e-8c24-4bf7-a627-1f291d6d2a9f" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="662986cd6941c04829d5352220b24469" ns2:_="" ns3:_="">
     <xsd:import namespace="c7208212-5067-493a-8683-cc3386cb0efe"/>
@@ -2094,15 +2144,6 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
   <documentManagement>
@@ -2160,6 +2201,14 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{393EE603-C983-481A-9007-FE0C7A6F709A}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{EAF2F9FC-3A71-42D2-842A-D0923E27A331}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -2178,14 +2227,6 @@
 </ds:datastoreItem>
 </file>
 
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{393EE603-C983-481A-9007-FE0C7A6F709A}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{1CD2B120-A90D-496C-8884-A2A9574072D6}">
   <ds:schemaRefs>

--- a/ZANSHIN/進捗コスト表.xlsx
+++ b/ZANSHIN/進捗コスト表.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\PC_User\Documents\GitHub\KengoSchoole\ZANSHIN\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{70A78409-24E6-4E6C-8C6E-03ED9F67D52F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F7928BF5-77DC-4471-9DEA-285A80772D43}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="2670" yWindow="3585" windowWidth="21600" windowHeight="11295" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="2445" yWindow="1590" windowWidth="21600" windowHeight="11295" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="仕様" sheetId="1" r:id="rId1"/>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="80" uniqueCount="50">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="81" uniqueCount="52">
   <si>
     <t>1コスト:3時間 (1日は基本2コスト)</t>
   </si>
@@ -214,34 +214,7 @@
     <phoneticPr fontId="1"/>
   </si>
   <si>
-    <t>・クラス設計</t>
-  </si>
-  <si>
     <t>未完</t>
-  </si>
-  <si>
-    <t>・ライブラリ設計</t>
-  </si>
-  <si>
-    <t>・アルファ素材集め</t>
-  </si>
-  <si>
-    <t>　ー　モデル</t>
-  </si>
-  <si>
-    <t>　ー　UI素材</t>
-  </si>
-  <si>
-    <t>　ー　SE</t>
-  </si>
-  <si>
-    <t>　ー　BGM</t>
-  </si>
-  <si>
-    <t>　ー　マップ素材</t>
-  </si>
-  <si>
-    <t>　ー　エフェクト</t>
   </si>
   <si>
     <t>未完</t>
@@ -284,13 +257,6 @@
   </si>
   <si>
     <t>ーガード</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>プレイヤーの仕様</t>
-    <rPh sb="6" eb="8">
-      <t>シヨウ</t>
-    </rPh>
     <phoneticPr fontId="1"/>
   </si>
   <si>
@@ -396,6 +362,90 @@
     <t>形態変化</t>
     <rPh sb="0" eb="4">
       <t>ケイタイヘンカ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>マップの作成</t>
+    <rPh sb="4" eb="6">
+      <t>サクセイ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>ゲームの流れの作成</t>
+    <rPh sb="4" eb="5">
+      <t>ナガ</t>
+    </rPh>
+    <rPh sb="7" eb="9">
+      <t>サクセイ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>ータイトルシーン</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>ークリアシーン</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>各キャラクターの動き</t>
+    <rPh sb="0" eb="1">
+      <t>カク</t>
+    </rPh>
+    <rPh sb="8" eb="9">
+      <t>ウゴ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>ーボスのアニメーション</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>ーボスの素材</t>
+    <rPh sb="4" eb="6">
+      <t>ソザイ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>ープレイヤーのアニメーション</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>ープレイヤーの素材</t>
+    <rPh sb="7" eb="9">
+      <t>ソザイ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>ー背景素材</t>
+    <rPh sb="1" eb="3">
+      <t>ハイケイ</t>
+    </rPh>
+    <rPh sb="3" eb="5">
+      <t>ソザイ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>ー足場配置</t>
+    <rPh sb="1" eb="5">
+      <t>アシバハイチ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>ー足場素材</t>
+    <rPh sb="1" eb="3">
+      <t>アシバ</t>
+    </rPh>
+    <rPh sb="3" eb="5">
+      <t>ソザイ</t>
     </rPh>
     <phoneticPr fontId="1"/>
   </si>
@@ -464,7 +514,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="14">
+  <fills count="12">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -527,18 +577,6 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFE699"/>
-        <bgColor rgb="FF000000"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF8CBAD"/>
-        <bgColor rgb="FF000000"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor theme="7" tint="0.39997558519241921"/>
         <bgColor indexed="64"/>
       </patternFill>
@@ -593,7 +631,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="24">
+  <cellXfs count="23">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="56" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="176" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
@@ -612,12 +650,11 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="4" fillId="11" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="4" fillId="12" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="13" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="11" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="標準" xfId="0" builtinId="0"/>
@@ -898,7 +935,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:L88"/>
+  <dimension ref="A1:L90"/>
   <sheetFormatPr defaultRowHeight="18.75"/>
   <cols>
     <col min="1" max="1" width="9.25" customWidth="1"/>
@@ -934,26 +971,22 @@
         <v>5</v>
       </c>
       <c r="H2">
-        <f>SUM(C3:C88)</f>
-        <v>24</v>
+        <f>SUM(C3:C90)</f>
+        <v>55</v>
       </c>
     </row>
     <row r="3" spans="1:12">
-      <c r="B3" s="18" t="s">
-        <v>20</v>
-      </c>
-      <c r="C3" s="18">
-        <v>3</v>
-      </c>
-      <c r="D3" s="18"/>
-      <c r="E3" s="18" t="s">
-        <v>30</v>
-      </c>
+      <c r="B3" s="22" t="s">
+        <v>41</v>
+      </c>
+      <c r="C3" s="22"/>
+      <c r="D3" s="22"/>
+      <c r="E3" s="22"/>
       <c r="G3" s="9" t="s">
         <v>6</v>
       </c>
       <c r="H3">
-        <f>SUMIF(E3:E88,"完了",C3:C88)</f>
+        <f>SUMIF(E3:E90,"完了",C3:C90)</f>
         <v>0</v>
       </c>
       <c r="K3" t="s">
@@ -964,22 +997,22 @@
       </c>
     </row>
     <row r="4" spans="1:12">
-      <c r="B4" s="19" t="s">
-        <v>22</v>
-      </c>
-      <c r="C4" s="19">
-        <v>8</v>
-      </c>
-      <c r="D4" s="19"/>
-      <c r="E4" s="19" t="s">
-        <v>30</v>
+      <c r="B4" s="20" t="s">
+        <v>42</v>
+      </c>
+      <c r="C4" s="20">
+        <v>3</v>
+      </c>
+      <c r="D4" s="20"/>
+      <c r="E4" s="20" t="s">
+        <v>20</v>
       </c>
       <c r="G4" s="10" t="s">
         <v>9</v>
       </c>
       <c r="H4" s="2">
         <f ca="1">NETWORKDAYS(H5,H6)</f>
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="I4" t="s">
         <v>10</v>
@@ -990,7 +1023,7 @@
       </c>
       <c r="K4" s="2">
         <f ca="1">_xlfn.DAYS(H6,H5)</f>
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="L4" s="3">
         <f ca="1">H3/K4</f>
@@ -998,12 +1031,16 @@
       </c>
     </row>
     <row r="5" spans="1:12">
-      <c r="B5" s="19" t="s">
-        <v>23</v>
-      </c>
-      <c r="C5" s="19"/>
-      <c r="D5" s="19"/>
-      <c r="E5" s="19"/>
+      <c r="B5" s="20" t="s">
+        <v>43</v>
+      </c>
+      <c r="C5" s="20">
+        <v>3</v>
+      </c>
+      <c r="D5" s="20"/>
+      <c r="E5" s="20" t="s">
+        <v>20</v>
+      </c>
       <c r="G5" s="11" t="s">
         <v>11</v>
       </c>
@@ -1013,83 +1050,75 @@
       </c>
     </row>
     <row r="6" spans="1:12">
-      <c r="B6" s="19" t="s">
-        <v>24</v>
-      </c>
-      <c r="C6" s="19">
-        <v>2</v>
-      </c>
-      <c r="D6" s="19"/>
-      <c r="E6" s="19" t="s">
-        <v>30</v>
-      </c>
+      <c r="B6" s="22" t="s">
+        <v>44</v>
+      </c>
+      <c r="C6" s="22"/>
+      <c r="D6" s="22"/>
+      <c r="E6" s="22"/>
       <c r="G6" s="12" t="s">
         <v>12</v>
       </c>
       <c r="H6" s="1">
         <f ca="1">TODAY()</f>
-        <v>46233</v>
+        <v>46234</v>
       </c>
     </row>
     <row r="7" spans="1:12">
-      <c r="B7" s="18" t="s">
-        <v>25</v>
-      </c>
-      <c r="C7" s="18">
+      <c r="B7" s="20" t="s">
+        <v>48</v>
+      </c>
+      <c r="C7" s="20">
         <v>2</v>
       </c>
-      <c r="D7" s="18"/>
-      <c r="E7" s="18" t="s">
-        <v>21</v>
+      <c r="D7" s="20"/>
+      <c r="E7" s="20" t="s">
+        <v>20</v>
       </c>
     </row>
     <row r="8" spans="1:12">
-      <c r="B8" s="18" t="s">
-        <v>26</v>
-      </c>
-      <c r="C8" s="18">
+      <c r="B8" s="20" t="s">
+        <v>47</v>
+      </c>
+      <c r="C8" s="20">
         <v>2</v>
       </c>
-      <c r="D8" s="18"/>
-      <c r="E8" s="18" t="s">
-        <v>21</v>
+      <c r="D8" s="20"/>
+      <c r="E8" s="20" t="s">
+        <v>20</v>
       </c>
     </row>
     <row r="9" spans="1:12">
-      <c r="B9" s="18" t="s">
-        <v>27</v>
-      </c>
-      <c r="C9" s="18">
-        <v>1</v>
-      </c>
-      <c r="D9" s="18"/>
-      <c r="E9" s="18" t="s">
-        <v>21</v>
+      <c r="B9" s="20" t="s">
+        <v>46</v>
+      </c>
+      <c r="C9" s="20">
+        <v>2</v>
+      </c>
+      <c r="D9" s="20"/>
+      <c r="E9" s="20" t="s">
+        <v>20</v>
       </c>
     </row>
     <row r="10" spans="1:12">
-      <c r="B10" s="18" t="s">
-        <v>28</v>
-      </c>
-      <c r="C10" s="18">
-        <v>1</v>
-      </c>
-      <c r="D10" s="18"/>
-      <c r="E10" s="18" t="s">
-        <v>21</v>
+      <c r="B10" s="20" t="s">
+        <v>45</v>
+      </c>
+      <c r="C10" s="20">
+        <v>2</v>
+      </c>
+      <c r="D10" s="20"/>
+      <c r="E10" s="20" t="s">
+        <v>20</v>
       </c>
     </row>
     <row r="11" spans="1:12">
-      <c r="B11" s="20" t="s">
-        <v>29</v>
-      </c>
-      <c r="C11" s="20">
-        <v>5</v>
-      </c>
-      <c r="D11" s="20"/>
-      <c r="E11" s="20" t="s">
-        <v>21</v>
-      </c>
+      <c r="B11" s="22" t="s">
+        <v>40</v>
+      </c>
+      <c r="C11" s="22"/>
+      <c r="D11" s="22"/>
+      <c r="E11" s="22"/>
       <c r="I11" t="s">
         <v>13</v>
       </c>
@@ -1104,13 +1133,15 @@
       </c>
     </row>
     <row r="12" spans="1:12">
-      <c r="B12" s="21" t="s">
-        <v>37</v>
-      </c>
-      <c r="C12" s="21"/>
-      <c r="D12" s="21"/>
-      <c r="E12" s="21" t="s">
-        <v>30</v>
+      <c r="B12" s="20" t="s">
+        <v>49</v>
+      </c>
+      <c r="C12" s="20">
+        <v>2</v>
+      </c>
+      <c r="D12" s="20"/>
+      <c r="E12" s="20" t="s">
+        <v>20</v>
       </c>
       <c r="G12" s="8" t="s">
         <v>17</v>
@@ -1121,29 +1152,31 @@
       </c>
       <c r="I12" s="2">
         <f ca="1">NETWORKDAYS(TODAY(),H12)</f>
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="J12" s="3">
         <f ca="1">($H$2 - $H$3) / I12</f>
-        <v>1.411764705882353</v>
+        <v>3.4375</v>
       </c>
       <c r="K12">
         <f ca="1">_xlfn.DAYS(H12,$H$6)</f>
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="L12" s="3">
         <f ca="1">($H$2 - $H$3) / K12</f>
-        <v>1</v>
+        <v>2.3913043478260869</v>
       </c>
     </row>
     <row r="13" spans="1:12">
-      <c r="B13" s="16" t="s">
-        <v>31</v>
-      </c>
-      <c r="C13" s="16"/>
-      <c r="D13" s="16"/>
-      <c r="E13" s="16" t="s">
-        <v>21</v>
+      <c r="B13" s="20" t="s">
+        <v>50</v>
+      </c>
+      <c r="C13" s="20">
+        <v>2</v>
+      </c>
+      <c r="D13" s="20"/>
+      <c r="E13" s="20" t="s">
+        <v>20</v>
       </c>
       <c r="G13" s="13" t="s">
         <v>18</v>
@@ -1154,29 +1187,31 @@
       </c>
       <c r="I13" s="2">
         <f t="shared" ref="I13:I14" ca="1" si="0">NETWORKDAYS(TODAY(),H13)</f>
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="J13" s="3">
         <f ca="1">($H$2 - $H$3) / I13</f>
-        <v>1.0909090909090908</v>
+        <v>2.6190476190476191</v>
       </c>
       <c r="K13">
         <f t="shared" ref="K13:K14" ca="1" si="1">_xlfn.DAYS(H13,$H$6)</f>
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="L13" s="3">
         <f ca="1">($H$2 - $H$3) / K13</f>
-        <v>0.77419354838709675</v>
+        <v>1.8333333333333333</v>
       </c>
     </row>
     <row r="14" spans="1:12">
-      <c r="B14" s="16" t="s">
-        <v>32</v>
-      </c>
-      <c r="C14" s="16"/>
-      <c r="D14" s="16"/>
-      <c r="E14" s="16" t="s">
-        <v>21</v>
+      <c r="B14" s="20" t="s">
+        <v>51</v>
+      </c>
+      <c r="C14" s="21">
+        <v>2</v>
+      </c>
+      <c r="D14" s="21"/>
+      <c r="E14" s="21" t="s">
+        <v>20</v>
       </c>
       <c r="G14" s="14" t="s">
         <v>19</v>
@@ -1187,30 +1222,28 @@
       </c>
       <c r="I14" s="2">
         <f t="shared" ca="1" si="0"/>
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="J14" s="3">
         <f ca="1">($H$2 - $H$3) / I14</f>
-        <v>1</v>
+        <v>2.3913043478260869</v>
       </c>
       <c r="K14">
         <f t="shared" ca="1" si="1"/>
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="L14" s="3">
         <f ca="1">($H$2 - $H$3) / K14</f>
-        <v>0.72727272727272729</v>
+        <v>1.71875</v>
       </c>
     </row>
     <row r="15" spans="1:12">
-      <c r="B15" s="16" t="s">
-        <v>33</v>
-      </c>
-      <c r="C15" s="16"/>
-      <c r="D15" s="16"/>
-      <c r="E15" s="16" t="s">
-        <v>21</v>
-      </c>
+      <c r="B15" s="18" t="s">
+        <v>22</v>
+      </c>
+      <c r="C15" s="18"/>
+      <c r="D15" s="18"/>
+      <c r="E15" s="18"/>
       <c r="G15" s="15"/>
       <c r="H15" s="1"/>
       <c r="I15" s="2"/>
@@ -1219,9 +1252,11 @@
     </row>
     <row r="16" spans="1:12">
       <c r="B16" s="16" t="s">
-        <v>34</v>
-      </c>
-      <c r="C16" s="16"/>
+        <v>23</v>
+      </c>
+      <c r="C16" s="16">
+        <v>2</v>
+      </c>
       <c r="D16" s="16"/>
       <c r="E16" s="16" t="s">
         <v>21</v>
@@ -1229,189 +1264,231 @@
     </row>
     <row r="17" spans="2:5">
       <c r="B17" s="16" t="s">
-        <v>35</v>
-      </c>
-      <c r="C17" s="16"/>
+        <v>24</v>
+      </c>
+      <c r="C17" s="16">
+        <v>2</v>
+      </c>
       <c r="D17" s="16"/>
       <c r="E17" s="16" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
     </row>
     <row r="18" spans="2:5">
       <c r="B18" s="16" t="s">
-        <v>36</v>
-      </c>
-      <c r="C18" s="16"/>
+        <v>25</v>
+      </c>
+      <c r="C18" s="16">
+        <v>2</v>
+      </c>
       <c r="D18" s="16"/>
       <c r="E18" s="16" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
     </row>
     <row r="19" spans="2:5">
       <c r="B19" s="16" t="s">
-        <v>48</v>
-      </c>
-      <c r="C19" s="16"/>
+        <v>26</v>
+      </c>
+      <c r="C19" s="16">
+        <v>1</v>
+      </c>
       <c r="D19" s="16"/>
       <c r="E19" s="16" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
     </row>
     <row r="20" spans="2:5">
       <c r="B20" s="16" t="s">
-        <v>43</v>
-      </c>
-      <c r="C20" s="16"/>
+        <v>27</v>
+      </c>
+      <c r="C20" s="16">
+        <v>1</v>
+      </c>
       <c r="D20" s="16"/>
       <c r="E20" s="16" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
     </row>
     <row r="21" spans="2:5">
       <c r="B21" s="16" t="s">
-        <v>42</v>
-      </c>
-      <c r="C21" s="16"/>
+        <v>38</v>
+      </c>
+      <c r="C21" s="16">
+        <v>2</v>
+      </c>
       <c r="D21" s="16"/>
       <c r="E21" s="16" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
     </row>
     <row r="22" spans="2:5">
-      <c r="B22" s="23" t="s">
-        <v>44</v>
-      </c>
-      <c r="C22" s="23"/>
-      <c r="D22" s="23"/>
-      <c r="E22" s="23"/>
+      <c r="B22" s="16" t="s">
+        <v>33</v>
+      </c>
+      <c r="C22" s="16">
+        <v>3</v>
+      </c>
+      <c r="D22" s="16"/>
+      <c r="E22" s="16" t="s">
+        <v>20</v>
+      </c>
     </row>
     <row r="23" spans="2:5">
       <c r="B23" s="16" t="s">
-        <v>45</v>
-      </c>
-      <c r="C23" s="16"/>
+        <v>32</v>
+      </c>
+      <c r="C23" s="16">
+        <v>4</v>
+      </c>
       <c r="D23" s="16"/>
       <c r="E23" s="16" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
     </row>
     <row r="24" spans="2:5">
-      <c r="B24" s="16" t="s">
-        <v>46</v>
-      </c>
-      <c r="C24" s="16"/>
-      <c r="D24" s="16"/>
-      <c r="E24" s="16" t="s">
-        <v>21</v>
-      </c>
+      <c r="B24" s="19" t="s">
+        <v>34</v>
+      </c>
+      <c r="C24" s="19"/>
+      <c r="D24" s="19"/>
+      <c r="E24" s="19"/>
     </row>
     <row r="25" spans="2:5">
       <c r="B25" s="16" t="s">
-        <v>47</v>
-      </c>
-      <c r="C25" s="16"/>
+        <v>35</v>
+      </c>
+      <c r="C25" s="16">
+        <v>1</v>
+      </c>
       <c r="D25" s="16"/>
       <c r="E25" s="16" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
     </row>
     <row r="26" spans="2:5">
-      <c r="B26" s="22" t="s">
-        <v>38</v>
-      </c>
-      <c r="C26" s="22"/>
-      <c r="D26" s="22"/>
-      <c r="E26" s="22"/>
+      <c r="B26" s="16" t="s">
+        <v>36</v>
+      </c>
+      <c r="C26" s="16">
+        <v>1</v>
+      </c>
+      <c r="D26" s="16"/>
+      <c r="E26" s="16" t="s">
+        <v>20</v>
+      </c>
     </row>
     <row r="27" spans="2:5">
       <c r="B27" s="16" t="s">
-        <v>39</v>
-      </c>
-      <c r="C27" s="16"/>
+        <v>37</v>
+      </c>
+      <c r="C27" s="16">
+        <v>1</v>
+      </c>
       <c r="D27" s="16"/>
       <c r="E27" s="16" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
     </row>
     <row r="28" spans="2:5">
-      <c r="B28" s="16" t="s">
-        <v>40</v>
-      </c>
-      <c r="C28" s="16"/>
-      <c r="D28" s="16"/>
-      <c r="E28" s="16" t="s">
-        <v>21</v>
-      </c>
+      <c r="B28" s="18" t="s">
+        <v>28</v>
+      </c>
+      <c r="C28" s="18"/>
+      <c r="D28" s="18"/>
+      <c r="E28" s="18"/>
     </row>
     <row r="29" spans="2:5">
       <c r="B29" s="16" t="s">
-        <v>41</v>
-      </c>
-      <c r="C29" s="16"/>
+        <v>29</v>
+      </c>
+      <c r="C29" s="16">
+        <v>2</v>
+      </c>
       <c r="D29" s="16"/>
       <c r="E29" s="16" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
     </row>
     <row r="30" spans="2:5">
       <c r="B30" s="16" t="s">
-        <v>42</v>
-      </c>
-      <c r="C30" s="16"/>
+        <v>30</v>
+      </c>
+      <c r="C30" s="16">
+        <v>2</v>
+      </c>
       <c r="D30" s="16"/>
       <c r="E30" s="16" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
     </row>
     <row r="31" spans="2:5">
       <c r="B31" s="16" t="s">
-        <v>49</v>
-      </c>
-      <c r="C31" s="16"/>
+        <v>31</v>
+      </c>
+      <c r="C31" s="16">
+        <v>3</v>
+      </c>
       <c r="D31" s="16"/>
       <c r="E31" s="16" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
     </row>
     <row r="32" spans="2:5">
-      <c r="B32" s="23" t="s">
-        <v>44</v>
-      </c>
-      <c r="C32" s="23"/>
-      <c r="D32" s="23"/>
-      <c r="E32" s="23"/>
+      <c r="B32" s="16" t="s">
+        <v>32</v>
+      </c>
+      <c r="C32" s="16">
+        <v>4</v>
+      </c>
+      <c r="D32" s="16"/>
+      <c r="E32" s="16" t="s">
+        <v>20</v>
+      </c>
     </row>
     <row r="33" spans="2:5">
       <c r="B33" s="16" t="s">
-        <v>45</v>
-      </c>
-      <c r="C33" s="16"/>
+        <v>39</v>
+      </c>
+      <c r="C33" s="16">
+        <v>2</v>
+      </c>
       <c r="D33" s="16"/>
       <c r="E33" s="16" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
     </row>
     <row r="34" spans="2:5">
-      <c r="B34" s="16" t="s">
-        <v>46</v>
-      </c>
-      <c r="C34" s="16"/>
-      <c r="D34" s="16"/>
-      <c r="E34" s="16" t="s">
-        <v>21</v>
-      </c>
+      <c r="B34" s="19" t="s">
+        <v>34</v>
+      </c>
+      <c r="C34" s="19"/>
+      <c r="D34" s="19"/>
+      <c r="E34" s="19"/>
     </row>
     <row r="35" spans="2:5">
-      <c r="B35" s="16"/>
-      <c r="C35" s="16"/>
+      <c r="B35" s="16" t="s">
+        <v>35</v>
+      </c>
+      <c r="C35" s="16">
+        <v>1</v>
+      </c>
       <c r="D35" s="16"/>
-      <c r="E35" s="16"/>
+      <c r="E35" s="16" t="s">
+        <v>20</v>
+      </c>
     </row>
     <row r="36" spans="2:5">
-      <c r="B36" s="16"/>
-      <c r="C36" s="16"/>
+      <c r="B36" s="16" t="s">
+        <v>36</v>
+      </c>
+      <c r="C36" s="16">
+        <v>1</v>
+      </c>
       <c r="D36" s="16"/>
-      <c r="E36" s="16"/>
+      <c r="E36" s="16" t="s">
+        <v>20</v>
+      </c>
     </row>
     <row r="37" spans="2:5">
       <c r="B37" s="16"/>
@@ -1682,10 +1759,10 @@
       <c r="E80" s="16"/>
     </row>
     <row r="81" spans="2:5">
-      <c r="B81" s="17"/>
-      <c r="C81" s="17"/>
-      <c r="D81" s="17"/>
-      <c r="E81" s="17"/>
+      <c r="B81" s="16"/>
+      <c r="C81" s="16"/>
+      <c r="D81" s="16"/>
+      <c r="E81" s="16"/>
     </row>
     <row r="82" spans="2:5">
       <c r="B82" s="16"/>
@@ -1694,10 +1771,10 @@
       <c r="E82" s="16"/>
     </row>
     <row r="83" spans="2:5">
-      <c r="B83" s="16"/>
-      <c r="C83" s="16"/>
-      <c r="D83" s="16"/>
-      <c r="E83" s="16"/>
+      <c r="B83" s="17"/>
+      <c r="C83" s="17"/>
+      <c r="D83" s="17"/>
+      <c r="E83" s="17"/>
     </row>
     <row r="84" spans="2:5">
       <c r="B84" s="16"/>
@@ -1728,6 +1805,18 @@
       <c r="C88" s="16"/>
       <c r="D88" s="16"/>
       <c r="E88" s="16"/>
+    </row>
+    <row r="89" spans="2:5">
+      <c r="B89" s="16"/>
+      <c r="C89" s="16"/>
+      <c r="D89" s="16"/>
+      <c r="E89" s="16"/>
+    </row>
+    <row r="90" spans="2:5">
+      <c r="B90" s="16"/>
+      <c r="C90" s="16"/>
+      <c r="D90" s="16"/>
+      <c r="E90" s="16"/>
     </row>
   </sheetData>
   <phoneticPr fontId="1"/>
@@ -1747,15 +1836,6 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="ドキュメント" ma:contentTypeID="0x010100916D42E3690EEE418172DBF4B6395129" ma:contentTypeVersion="32" ma:contentTypeDescription="新しいドキュメントを作成します。" ma:contentTypeScope="" ma:versionID="2bec52062c397840dce5bfa38caf7040">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="c7208212-5067-493a-8683-cc3386cb0efe" xmlns:ns3="b9cacb4e-8c24-4bf7-a627-1f291d6d2a9f" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="662986cd6941c04829d5352220b24469" ns2:_="" ns3:_="">
     <xsd:import namespace="c7208212-5067-493a-8683-cc3386cb0efe"/>
@@ -2144,6 +2224,15 @@
 </ct:contentTypeSchema>
 </file>
 
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
   <documentManagement>
@@ -2201,14 +2290,6 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{393EE603-C983-481A-9007-FE0C7A6F709A}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{EAF2F9FC-3A71-42D2-842A-D0923E27A331}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -2227,6 +2308,14 @@
 </ds:datastoreItem>
 </file>
 
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{393EE603-C983-481A-9007-FE0C7A6F709A}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{1CD2B120-A90D-496C-8884-A2A9574072D6}">
   <ds:schemaRefs>
